--- a/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
+++ b/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
@@ -5440,11 +5440,6 @@
           <t>3:21.960</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -16934,11 +16929,6 @@
           <t>1:53.026</t>
         </is>
       </c>
-      <c r="R262" t="inlineStr">
-        <is>
-          <t>64343</t>
-        </is>
-      </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>35556</t>
@@ -31598,11 +31588,6 @@
           <t>1:57.432</t>
         </is>
       </c>
-      <c r="R496" t="inlineStr">
-        <is>
-          <t>64343</t>
-        </is>
-      </c>
       <c r="S496" t="inlineStr">
         <is>
           <t>35556</t>
@@ -36343,11 +36328,6 @@
       <c r="P570" t="inlineStr">
         <is>
           <t>3:26.037</t>
-        </is>
-      </c>
-      <c r="R570" t="inlineStr">
-        <is>
-          <t>41785</t>
         </is>
       </c>
     </row>
@@ -49474,7 +49454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49788,17 +49768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>41785</t>
+          <t>47495</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Olivier</t>
+          <t>Iosif</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CAUWENBERGH</t>
+          <t>CHIRILA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -49810,61 +49790,61 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>47495</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Iosif</t>
+          <t>Stefania</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CHIRILA</t>
+          <t>CICALI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stefania</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CICALI</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>47443</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Dan Cristian</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>COSTEA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -49876,17 +49856,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>35782</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dan Cristian</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>COSTEA</t>
+          <t>DAVIDEK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -49898,17 +49878,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>35782</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DAVIDEK</t>
+          <t>DVORAK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -49920,17 +49900,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Filip</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DVORAK</t>
+          <t>DYACHENKO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -49942,61 +49922,61 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>42337</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Henriette Engel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DYACHENKO</t>
+          <t>HANSEN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Henriette Engel</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HANSEN</t>
+          <t>GELLE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>64343</t>
+          <t>56336</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Petr</t>
+          <t>Vyacheslav</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FUKSA</t>
+          <t>GORN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -50008,17 +49988,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>44434</t>
+          <t>35318</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Mathieu</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GELLE</t>
+          <t>GOUBEL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -50030,17 +50010,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>56336</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vyacheslav</t>
+          <t>Marcin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GORN</t>
+          <t>GRZYBOWSKI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -50052,17 +50032,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>35318</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mathieu</t>
+          <t>Dzianis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GOUBEL</t>
+          <t>HARAZHA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -50074,39 +50054,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Bridgitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GRZYBOWSKI</t>
+          <t>HARTLEY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>42042</t>
+          <t>52230</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dzianis</t>
+          <t>Mirziyodjon</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HARAZHA</t>
+          <t>KHOJIEV</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -50118,61 +50098,61 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>42336</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bridgitte</t>
+          <t>Rene Holten</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HARTLEY</t>
+          <t>POULSEN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>52230</t>
+          <t>35908</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mirziyodjon</t>
+          <t>Lenka</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KHOJIEV</t>
+          <t>HROCHOVA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>42336</t>
+          <t>35323</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rene Holten</t>
+          <t>Etienne</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>POULSEN</t>
+          <t>HUBERT</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -50184,39 +50164,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>35908</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lenka</t>
+          <t>Gabor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HROCHOVA</t>
+          <t>JAKUBIK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35323</t>
+          <t>49732</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Etienne</t>
+          <t>Tomas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HUBERT</t>
+          <t>JEZEK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -50228,17 +50208,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>44425</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gabor</t>
+          <t>Sebastien</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JAKUBIK</t>
+          <t>JOUVE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -50250,17 +50230,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49732</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tomas</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JEZEK</t>
+          <t>KACZOR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -50272,105 +50252,105 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>35328</t>
+          <t>45330</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sebastien</t>
+          <t>Shiho</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>JOUVE</t>
+          <t>KAKIZAKI</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>44421</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Ivana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KACZOR</t>
+          <t>KMETOVA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Shiho</t>
+          <t>Gerasim</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KAKIZAKI</t>
+          <t>KOCHNEV</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>44421</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ivana</t>
+          <t>Takayuki</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KMETOVA</t>
+          <t>KOKAJI</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Gerasim</t>
+          <t>Mariusz</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KOCHNEV</t>
+          <t>KUJAWSKI</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -50382,17 +50362,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Takayuki</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KOKAJI</t>
+          <t>KULETA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -50404,105 +50384,105 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>35880</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mariusz</t>
+          <t>Ana-Roxana</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KUJAWSKI</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>36165</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Natalia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KULETA</t>
+          <t>LOBOVA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>42364</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ana-Roxana</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LUNACEK</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>36185</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Kirill</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LOBOVA</t>
+          <t>LYAPUNOV</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>42364</t>
+          <t>42044</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Vadzim</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LUNACEK</t>
+          <t>MAKHNEU</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -50514,17 +50494,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>36185</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kirill</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LYAPUNOV</t>
+          <t>MARON</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -50536,39 +50516,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vadzim</t>
+          <t>Lucie</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MAKHNEU</t>
+          <t>MATOUSKOVA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>45290</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Momotaro</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MARON</t>
+          <t>MATSUSHITA</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -50580,39 +50560,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lucie</t>
+          <t>Vadim</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MATOUSKOVA</t>
+          <t>MENKOV</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>45290</t>
+          <t>52229</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Momotaro</t>
+          <t>Serik</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MATSUSHITA</t>
+          <t>MIRBEKOV</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -50624,17 +50604,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>47261</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vadim</t>
+          <t>Ionut</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MENKOV</t>
+          <t>MITREA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -50646,17 +50626,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>45293</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Serik</t>
+          <t>Keiji</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MIRBEKOV</t>
+          <t>MIZUMOTO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -50668,17 +50648,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>47261</t>
+          <t>35556</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ionut</t>
+          <t>Radek</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MITREA</t>
+          <t>MISKOVSKY</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -50690,39 +50670,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>45293</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Keiji</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MIZUMOTO</t>
+          <t>MURABITO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>36796</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Radek</t>
+          <t>Ricardas</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MISKOVSKY</t>
+          <t>NEKRIOSIUS</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -50734,17 +50714,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>45837</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MURABITO</t>
+          <t>NICHOLLS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -50756,17 +50736,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ricardas</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NEKRIOSIUS</t>
+          <t>ODVARKO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -50778,17 +50758,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>45329</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Asumi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NICHOLLS</t>
+          <t>OHMURA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -50800,17 +50780,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>36797</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Andrej</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ODVARKO</t>
+          <t>OLIJNIK</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -50822,39 +50802,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>45329</t>
+          <t>41784</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Asumi</t>
+          <t>Laurens</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OHMURA</t>
+          <t>PANNECOUCKE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>36797</t>
+          <t>49617</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Andrej</t>
+          <t>Matous</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OLIJNIK</t>
+          <t>PAVLIK</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -50866,17 +50846,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>41784</t>
+          <t>36163</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Laurens</t>
+          <t>Pavel</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PANNECOUCKE</t>
+          <t>PETROV</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -50888,17 +50868,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>45847</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Matous</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PAVLIK</t>
+          <t>PHILLIPS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -50910,17 +50890,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>36163</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pavel</t>
+          <t>Raman</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PETROV</t>
+          <t>PIATRUSHENKA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -50932,17 +50912,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>42052</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Dzmitry</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PHILLIPS</t>
+          <t>RABCHANKA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -50954,17 +50934,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>41991</t>
+          <t>35549</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Raman</t>
+          <t>Jaroslav</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PIATRUSHENKA</t>
+          <t>RADON</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -50976,17 +50956,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>42052</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dzmitry</t>
+          <t>Alberto</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>RABCHANKA</t>
+          <t>RICCHETTI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -50998,17 +50978,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>35549</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jaroslav</t>
+          <t>Aleksejs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RADON</t>
+          <t>RUMJANCEVS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -51020,17 +51000,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>36446</t>
+          <t>45294</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Alberto</t>
+          <t>Naoya</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RICCHETTI</t>
+          <t>SAKAMOTO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -51042,39 +51022,39 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>36593</t>
+          <t>36170</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Aleksejs</t>
+          <t>Iuliana</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RUMJANCEVS</t>
+          <t>SALAKHOVA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>45294</t>
+          <t>175299</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Naoya</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SAKAMOTO</t>
+          <t>SAYADI KACHALAKI</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -51086,17 +51066,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>36170</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Iuliana</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SALAKHOVA</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -51108,39 +51088,39 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>175299</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Viktoria</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SAYADI KACHALAKI</t>
+          <t>SCHWARZ</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>56337</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Ekaterina</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>SHUBINA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -51152,61 +51132,61 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Viktoria</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SCHWARZ</t>
+          <t>SIEMIONOWSKI</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>56337</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ekaterina</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SHUBINA</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>42341</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Emil Staer</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SIEMIONOWSKI</t>
+          <t>SIMENSEN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -51218,17 +51198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>STEWART</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -51240,17 +51220,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>42341</t>
+          <t>36792</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Emil Staer</t>
+          <t>Jevgenij</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SIMENSEN</t>
+          <t>SHUKLIN</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -51262,17 +51242,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>103499</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Issei</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>STEWART</t>
+          <t>TAKENAKA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -51284,17 +51264,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>36792</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jevgenij</t>
+          <t>Lukas</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SHUKLIN</t>
+          <t>TREFIL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -51306,17 +51286,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>103499</t>
+          <t>42054</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Issei</t>
+          <t>Dzmitry</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TAKENAKA</t>
+          <t>VAITSISHKIN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -51328,17 +51308,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lukas</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TREFIL</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -51350,17 +51330,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>42054</t>
+          <t>42053</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dzmitry</t>
+          <t>Aliaksandr</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>VAITSISHKIN</t>
+          <t>VAUCHETSKI</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -51372,83 +51352,83 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>35855</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Marta</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>WALCZYKIEWICZ</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>42053</t>
+          <t>42209</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Aliaksandr</t>
+          <t>Bernadette</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>VAUCHETSKI</t>
+          <t>WALLACE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>35855</t>
+          <t>42443</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WALCZYKIEWICZ</t>
+          <t>WATKINS</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>42209</t>
+          <t>35558</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bernadette</t>
+          <t>Ewelina</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>WALLACE</t>
+          <t>WOJNAROWSKA</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -51460,130 +51440,86 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>69210</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WATKINS</t>
+          <t>WRIGHT</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>35558</t>
+          <t>36149</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ewelina</t>
+          <t>Vitaly</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>WOJNAROWSKA</t>
+          <t>YURCHENKO</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>69210</t>
+          <t>35776</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Jan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>WRIGHT</t>
+          <t>STERBA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>36149</t>
+          <t>35550</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Vitaly</t>
+          <t>Filip</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>YURCHENKO</t>
+          <t>SVAB</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>35776</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>STERBA</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>35550</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Filip</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>SVAB</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
+++ b/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
@@ -1227,6 +1227,11 @@
           <t>3:49.851</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>36205</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1657,6 +1662,11 @@
           <t>3:48.151</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2162,6 +2172,11 @@
           <t>3:50.104</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3521,6 +3536,11 @@
           <t>4:18.452</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5380,6 +5400,11 @@
           <t>3:40.132</t>
         </is>
       </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6530,6 +6555,11 @@
           <t>36163</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8120,6 +8150,11 @@
           <t>36185</t>
         </is>
       </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>36149</t>
@@ -8920,6 +8955,11 @@
           <t>36446</t>
         </is>
       </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -11205,6 +11245,11 @@
           <t>1:45.637</t>
         </is>
       </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12069,6 +12114,11 @@
           <t>1:51.863</t>
         </is>
       </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -13179,6 +13229,11 @@
           <t>2:02.795</t>
         </is>
       </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14974,6 +15029,11 @@
           <t>1:33.781</t>
         </is>
       </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>47596</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -15284,6 +15344,11 @@
           <t>1:32.788</t>
         </is>
       </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -15534,6 +15599,11 @@
           <t>1:34.331</t>
         </is>
       </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -15594,6 +15664,11 @@
           <t>1:36.084</t>
         </is>
       </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -17119,6 +17194,11 @@
           <t>1:41.430</t>
         </is>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -19339,6 +19419,11 @@
           <t>3:32.159</t>
         </is>
       </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -19894,6 +19979,11 @@
           <t>3:33.929</t>
         </is>
       </c>
+      <c r="R309" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -20074,6 +20164,11 @@
           <t>3:43.618</t>
         </is>
       </c>
+      <c r="R312" t="inlineStr">
+        <is>
+          <t>36205</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -20683,6 +20778,11 @@
           <t>4:06.259</t>
         </is>
       </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -23428,6 +23528,11 @@
           <t>3:29.226</t>
         </is>
       </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -23753,6 +23858,11 @@
           <t>36163</t>
         </is>
       </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -24638,6 +24748,11 @@
           <t>36446</t>
         </is>
       </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -25983,6 +26098,11 @@
           <t>1:49.473</t>
         </is>
       </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -27238,6 +27358,11 @@
           <t>1:58.559</t>
         </is>
       </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -28093,6 +28218,11 @@
           <t>2:02.032</t>
         </is>
       </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -29763,6 +29893,11 @@
           <t>1:36.351</t>
         </is>
       </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -30023,6 +30158,11 @@
           <t>1:32.521</t>
         </is>
       </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -30083,6 +30223,11 @@
           <t>1:33.091</t>
         </is>
       </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>47596</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -30468,6 +30613,11 @@
           <t>1:38.987</t>
         </is>
       </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -32548,6 +32698,11 @@
           <t>3:48.698</t>
         </is>
       </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>36205</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -33116,6 +33271,11 @@
           <t>4:21.408</t>
         </is>
       </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -34912,6 +35072,11 @@
           <t>3:45.038</t>
         </is>
       </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -35097,6 +35262,11 @@
       <c r="L551" t="n">
         <v>1</v>
       </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="X551" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -38469,6 +38639,11 @@
           <t>36446</t>
         </is>
       </c>
+      <c r="T602" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -38536,6 +38711,11 @@
           <t>36185</t>
         </is>
       </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
       <c r="U603" t="inlineStr">
         <is>
           <t>36149</t>
@@ -40774,6 +40954,11 @@
           <t>1:55.562</t>
         </is>
       </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -41228,6 +41413,11 @@
           <t>1:32.271</t>
         </is>
       </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -43141,6 +43331,11 @@
           <t>1:51.733</t>
         </is>
       </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -44116,6 +44311,11 @@
           <t>1:29.458</t>
         </is>
       </c>
+      <c r="S688" t="inlineStr">
+        <is>
+          <t>47596</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -44240,6 +44440,11 @@
           <t>1:29.922</t>
         </is>
       </c>
+      <c r="S690" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -44488,6 +44693,11 @@
           <t>1:38.974</t>
         </is>
       </c>
+      <c r="S694" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -47581,6 +47791,11 @@
           <t>22:20.1</t>
         </is>
       </c>
+      <c r="R746" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -47973,6 +48188,11 @@
           <t>18:09.0</t>
         </is>
       </c>
+      <c r="R753" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -48531,6 +48751,11 @@
       <c r="P763" t="inlineStr">
         <is>
           <t>19:16.7</t>
+        </is>
+      </c>
+      <c r="R763" t="inlineStr">
+        <is>
+          <t>36205</t>
         </is>
       </c>
     </row>
@@ -49454,7 +49679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51525,6 +51750,204 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>36146</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ANOSHKIN</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>36155</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ivan</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SHTYL</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>36205</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Dmitrii</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>EKIMOV</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>42429</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Mauro</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>PRA FLORIANI</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>47596</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Petrus</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>GAVRILA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>52756</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Shahou</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>NASERI</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
+++ b/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
@@ -5465,6 +5465,11 @@
           <t>3:21.960</t>
         </is>
       </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -17004,6 +17009,11 @@
           <t>1:53.026</t>
         </is>
       </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>64343</t>
+        </is>
+      </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>35556</t>
@@ -31738,6 +31748,11 @@
           <t>1:57.432</t>
         </is>
       </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>64343</t>
+        </is>
+      </c>
       <c r="S496" t="inlineStr">
         <is>
           <t>35556</t>
@@ -36498,6 +36513,11 @@
       <c r="P570" t="inlineStr">
         <is>
           <t>3:26.037</t>
+        </is>
+      </c>
+      <c r="R570" t="inlineStr">
+        <is>
+          <t>41785</t>
         </is>
       </c>
     </row>
@@ -49679,7 +49699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51948,6 +51968,50 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>41785</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Olivier</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CAUWENBERGH</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>64343</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Petr</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FUKSA</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
+++ b/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
@@ -5465,11 +5465,6 @@
           <t>3:21.960</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -17009,11 +17004,6 @@
           <t>1:53.026</t>
         </is>
       </c>
-      <c r="R262" t="inlineStr">
-        <is>
-          <t>64343</t>
-        </is>
-      </c>
       <c r="S262" t="inlineStr">
         <is>
           <t>35556</t>
@@ -31748,11 +31738,6 @@
           <t>1:57.432</t>
         </is>
       </c>
-      <c r="R496" t="inlineStr">
-        <is>
-          <t>64343</t>
-        </is>
-      </c>
       <c r="S496" t="inlineStr">
         <is>
           <t>35556</t>
@@ -36513,11 +36498,6 @@
       <c r="P570" t="inlineStr">
         <is>
           <t>3:26.037</t>
-        </is>
-      </c>
-      <c r="R570" t="inlineStr">
-        <is>
-          <t>41785</t>
         </is>
       </c>
     </row>
@@ -49699,7 +49679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51968,50 +51948,6 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>41785</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Olivier</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>CAUWENBERGH</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>64343</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Petr</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>FUKSA</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
+++ b/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
@@ -8680,6 +8680,11 @@
           <t>2:58.583</t>
         </is>
       </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>35380</t>
+        </is>
+      </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>35296</t>
@@ -38292,6 +38297,11 @@
       <c r="P597" t="inlineStr">
         <is>
           <t>3:00.679</t>
+        </is>
+      </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>35380</t>
         </is>
       </c>
       <c r="S597" t="inlineStr">
@@ -49679,7 +49689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51948,6 +51958,28 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>35380</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Vincent</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>LECRUIBIER</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
+++ b/events/Racice_2009_WC/Racice_2009_WC_Results.xlsx
@@ -2982,6 +2982,11 @@
           <t>4:21.955</t>
         </is>
       </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13109,6 +13114,11 @@
           <t>1:57.169</t>
         </is>
       </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -21423,6 +21433,11 @@
           <t>4:28.967</t>
         </is>
       </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -27548,6 +27563,11 @@
           <t>2:01.878</t>
         </is>
       </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -40585,6 +40605,11 @@
       <c r="P631" t="inlineStr">
         <is>
           <t>1:52.623</t>
+        </is>
+      </c>
+      <c r="R631" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
     </row>
@@ -49689,7 +49714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51980,6 +52005,28 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Nivalter</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SANTOS DE JESUS</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
